--- a/关键词/词包上传模版.xlsx
+++ b/关键词/词包上传模版.xlsx
@@ -128,16 +128,16 @@
     <t>匹配方式（选填）</t>
   </si>
   <si>
-    <t>金夫人婚纱照</t>
-  </si>
-  <si>
-    <t>金夫人婚纱摄影真实评价</t>
-  </si>
-  <si>
-    <t>金夫人婚纱摄影</t>
-  </si>
-  <si>
-    <t>婚纱照风格推荐金夫人</t>
+    <t>示例婚纱照</t>
+  </si>
+  <si>
+    <t>示例婚纱摄影真实评价</t>
+  </si>
+  <si>
+    <t>示例婚纱摄影</t>
+  </si>
+  <si>
+    <t>婚纱照风格推荐示例</t>
   </si>
   <si>
     <t>婚纱照</t>
